--- a/data/BD Campaña San Juan.xlsx
+++ b/data/BD Campaña San Juan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jescalera\Documents\SAN JUAN DASHBOARD\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E8A52C-02AE-4668-BC57-3C3B6E81F7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E97168-AB68-4A91-8326-04D8B5114E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{195A31B7-CEAF-4C8B-96A9-10FB87544323}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Base" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$N$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$N$236</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="269">
   <si>
     <t>Fecha</t>
   </si>
@@ -700,6 +700,153 @@
   </si>
   <si>
     <t>003423</t>
+  </si>
+  <si>
+    <t>003426</t>
+  </si>
+  <si>
+    <t>062980</t>
+  </si>
+  <si>
+    <t>062981</t>
+  </si>
+  <si>
+    <t>062987</t>
+  </si>
+  <si>
+    <t>062989</t>
+  </si>
+  <si>
+    <t>003153</t>
+  </si>
+  <si>
+    <t>000536</t>
+  </si>
+  <si>
+    <t>000537</t>
+  </si>
+  <si>
+    <t>000540</t>
+  </si>
+  <si>
+    <t>003169</t>
+  </si>
+  <si>
+    <t>003170</t>
+  </si>
+  <si>
+    <t>003171</t>
+  </si>
+  <si>
+    <t>003177</t>
+  </si>
+  <si>
+    <t>003440</t>
+  </si>
+  <si>
+    <t>063018</t>
+  </si>
+  <si>
+    <t>003448</t>
+  </si>
+  <si>
+    <t>003449</t>
+  </si>
+  <si>
+    <t>000542</t>
+  </si>
+  <si>
+    <t>000544</t>
+  </si>
+  <si>
+    <t>003465</t>
+  </si>
+  <si>
+    <t>003466</t>
+  </si>
+  <si>
+    <t>003187</t>
+  </si>
+  <si>
+    <t>003193</t>
+  </si>
+  <si>
+    <t>003477</t>
+  </si>
+  <si>
+    <t>003484</t>
+  </si>
+  <si>
+    <t>003195</t>
+  </si>
+  <si>
+    <t>000549</t>
+  </si>
+  <si>
+    <t>003198</t>
+  </si>
+  <si>
+    <t>003201</t>
+  </si>
+  <si>
+    <t>000552</t>
+  </si>
+  <si>
+    <t>000553</t>
+  </si>
+  <si>
+    <t>003213</t>
+  </si>
+  <si>
+    <t>003229</t>
+  </si>
+  <si>
+    <t>000556</t>
+  </si>
+  <si>
+    <t>003236</t>
+  </si>
+  <si>
+    <t>003491</t>
+  </si>
+  <si>
+    <t>003493</t>
+  </si>
+  <si>
+    <t>003495</t>
+  </si>
+  <si>
+    <t>062982</t>
+  </si>
+  <si>
+    <t>000534</t>
+  </si>
+  <si>
+    <t>000538</t>
+  </si>
+  <si>
+    <t>003172</t>
+  </si>
+  <si>
+    <t>003459</t>
+  </si>
+  <si>
+    <t>003486</t>
+  </si>
+  <si>
+    <t>003227</t>
+  </si>
+  <si>
+    <t>003232</t>
+  </si>
+  <si>
+    <t>003498</t>
+  </si>
+  <si>
+    <t>063022</t>
+  </si>
+  <si>
+    <t>003499</t>
   </si>
 </sst>
 </file>
@@ -846,10 +993,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10374E95-5D2C-4793-97BF-BE592FBD4129}" name="BD" displayName="BD" ref="A1:N187" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:N187" xr:uid="{96A8FB89-0BFB-4212-8B86-7443EF4F1B7D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N7">
-    <sortCondition ref="A1:A7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10374E95-5D2C-4793-97BF-BE592FBD4129}" name="BD" displayName="BD" ref="A1:N236" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N236" xr:uid="{96A8FB89-0BFB-4212-8B86-7443EF4F1B7D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N236">
+    <sortCondition descending="1" ref="J1:J236"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{E0617225-4DD1-4A0C-B351-A45F4B1AF696}" name="Fecha" dataDxfId="13"/>
@@ -1168,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A8FB89-0BFB-4212-8B86-7443EF4F1B7D}">
-  <dimension ref="A1:N187"/>
+  <dimension ref="A1:N236"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
@@ -1230,7 +1377,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>177</v>
@@ -1251,30 +1398,30 @@
         <v>15</v>
       </c>
       <c r="J2" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K2" s="4">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L2" s="4">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="M2" s="4">
-        <v>43.5</v>
+        <v>130.5</v>
       </c>
       <c r="N2" s="4">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
-        <v>46191</v>
+        <v>46193</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>177</v>
@@ -1312,13 +1459,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>177</v>
@@ -1339,19 +1486,19 @@
         <v>15</v>
       </c>
       <c r="J4" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4" s="4">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L4" s="4">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="M4" s="4">
-        <v>21.75</v>
+        <v>87</v>
       </c>
       <c r="N4" s="4">
-        <v>0.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -1362,7 +1509,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>181</v>
@@ -1383,19 +1530,19 @@
         <v>15</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L5" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M5" s="4">
-        <v>21.75</v>
+        <v>65.25</v>
       </c>
       <c r="N5" s="4">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1406,7 +1553,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>181</v>
@@ -1450,7 +1597,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>181</v>
@@ -1471,19 +1618,19 @@
         <v>15</v>
       </c>
       <c r="J7" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L7" s="4">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M7" s="4">
-        <v>43.5</v>
+        <v>65.25</v>
       </c>
       <c r="N7" s="4">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1494,7 +1641,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>181</v>
@@ -1515,19 +1662,19 @@
         <v>15</v>
       </c>
       <c r="J8" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L8" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M8" s="4">
-        <v>21.75</v>
+        <v>65.25</v>
       </c>
       <c r="N8" s="4">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1538,7 +1685,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>181</v>
@@ -1559,19 +1706,19 @@
         <v>15</v>
       </c>
       <c r="J9" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L9" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M9" s="4">
-        <v>21.75</v>
+        <v>65.25</v>
       </c>
       <c r="N9" s="4">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1582,7 +1729,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>181</v>
@@ -1626,7 +1773,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>181</v>
@@ -1647,74 +1794,74 @@
         <v>15</v>
       </c>
       <c r="J11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L11" s="4">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M11" s="4">
-        <v>43.5</v>
+        <v>65.25</v>
       </c>
       <c r="N11" s="4">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J12" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L12" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M12" s="4">
-        <v>21.75</v>
+        <v>65.25</v>
       </c>
       <c r="N12" s="4">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>181</v>
@@ -1752,13 +1899,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>181</v>
@@ -1779,30 +1926,30 @@
         <v>15</v>
       </c>
       <c r="J14" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K14" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L14" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M14" s="4">
-        <v>21.75</v>
+        <v>65.25</v>
       </c>
       <c r="N14" s="4">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>181</v>
@@ -1823,36 +1970,36 @@
         <v>15</v>
       </c>
       <c r="J15" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L15" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M15" s="4">
-        <v>21.75</v>
+        <v>65.25</v>
       </c>
       <c r="N15" s="4">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>31</v>
+        <v>161</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>182</v>
@@ -1861,36 +2008,36 @@
         <v>183</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J16" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L16" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M16" s="4">
-        <v>21.75</v>
+        <v>65.25</v>
       </c>
       <c r="N16" s="4">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>181</v>
@@ -1911,30 +2058,30 @@
         <v>15</v>
       </c>
       <c r="J17" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K17" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L17" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M17" s="4">
-        <v>21.75</v>
+        <v>65.25</v>
       </c>
       <c r="N17" s="4">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>34</v>
+        <v>168</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>181</v>
@@ -1955,30 +2102,30 @@
         <v>15</v>
       </c>
       <c r="J18" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L18" s="4">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M18" s="4">
-        <v>43.5</v>
+        <v>65.25</v>
       </c>
       <c r="N18" s="4">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>35</v>
+        <v>218</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>181</v>
@@ -1999,36 +2146,36 @@
         <v>15</v>
       </c>
       <c r="J19" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L19" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M19" s="4">
-        <v>21.75</v>
+        <v>65.25</v>
       </c>
       <c r="N19" s="4">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
-        <v>46192</v>
+        <v>46197</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>36</v>
+        <v>267</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>182</v>
@@ -2037,42 +2184,42 @@
         <v>183</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J20" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L20" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M20" s="4">
-        <v>21.75</v>
+        <v>65.25</v>
       </c>
       <c r="N20" s="4">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>37</v>
+        <v>268</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>182</v>
@@ -2081,69 +2228,69 @@
         <v>183</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J21" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L21" s="4">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M21" s="4">
-        <v>21.75</v>
+        <v>65.25</v>
       </c>
       <c r="N21" s="4">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J22" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L22" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M22" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N22" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -2151,16 +2298,16 @@
         <v>46192</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>182</v>
@@ -2169,7 +2316,7 @@
         <v>183</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>15</v>
@@ -2195,16 +2342,16 @@
         <v>46192</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>182</v>
@@ -2213,25 +2360,25 @@
         <v>183</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J24" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L24" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M24" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N24" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2239,16 +2386,16 @@
         <v>46192</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>182</v>
@@ -2257,25 +2404,25 @@
         <v>183</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J25" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L25" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M25" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N25" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2283,43 +2430,43 @@
         <v>46192</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J26" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" s="4">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L26" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M26" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N26" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2330,7 +2477,7 @@
         <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>181</v>
@@ -2351,19 +2498,19 @@
         <v>15</v>
       </c>
       <c r="J27" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L27" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M27" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N27" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2371,16 +2518,16 @@
         <v>46192</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>182</v>
@@ -2389,25 +2536,25 @@
         <v>183</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J28" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L28" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M28" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N28" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2415,16 +2562,16 @@
         <v>46192</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>182</v>
@@ -2433,25 +2580,25 @@
         <v>183</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J29" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L29" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M29" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N29" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2459,43 +2606,43 @@
         <v>46192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J30" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L30" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M30" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N30" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2506,7 +2653,7 @@
         <v>18</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>181</v>
@@ -2527,19 +2674,19 @@
         <v>15</v>
       </c>
       <c r="J31" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L31" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M31" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N31" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2547,16 +2694,16 @@
         <v>46192</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>182</v>
@@ -2565,25 +2712,25 @@
         <v>183</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J32" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L32" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M32" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N32" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2591,186 +2738,186 @@
         <v>46192</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J33" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L33" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M33" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N33" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="4">
+        <v>2</v>
+      </c>
+      <c r="K34" s="4">
+        <v>8</v>
+      </c>
+      <c r="L34" s="4">
         <v>50</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="4">
-        <v>1</v>
-      </c>
-      <c r="K34" s="4">
-        <v>6</v>
-      </c>
-      <c r="L34" s="4">
-        <v>25</v>
-      </c>
       <c r="M34" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N34" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J35" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K35" s="4">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L35" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M35" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N35" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J36" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L36" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M36" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N36" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>181</v>
@@ -2791,36 +2938,36 @@
         <v>15</v>
       </c>
       <c r="J37" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L37" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M37" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N37" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>182</v>
@@ -2829,42 +2976,42 @@
         <v>183</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J38" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L38" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M38" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N38" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>178</v>
@@ -2873,36 +3020,36 @@
         <v>179</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J39" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L39" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M39" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N39" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>181</v>
@@ -2923,30 +3070,30 @@
         <v>15</v>
       </c>
       <c r="J40" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40" s="4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L40" s="4">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M40" s="4">
-        <v>65.25</v>
+        <v>43.5</v>
       </c>
       <c r="N40" s="4">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>57</v>
+        <v>170</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>181</v>
@@ -2967,30 +3114,30 @@
         <v>15</v>
       </c>
       <c r="J41" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K41" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L41" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M41" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N41" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>181</v>
@@ -3011,30 +3158,30 @@
         <v>15</v>
       </c>
       <c r="J42" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L42" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M42" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N42" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>59</v>
+        <v>173</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>181</v>
@@ -3055,36 +3202,36 @@
         <v>15</v>
       </c>
       <c r="J43" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L43" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M43" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N43" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>60</v>
+        <v>196</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>182</v>
@@ -3093,7 +3240,7 @@
         <v>183</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>15</v>
@@ -3116,19 +3263,19 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>61</v>
+        <v>199</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>182</v>
@@ -3137,36 +3284,36 @@
         <v>183</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J45" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L45" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M45" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N45" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>62</v>
+        <v>201</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>185</v>
@@ -3187,36 +3334,36 @@
         <v>15</v>
       </c>
       <c r="J46" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L46" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M46" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N46" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>63</v>
+        <v>202</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>182</v>
@@ -3225,42 +3372,42 @@
         <v>183</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J47" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L47" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M47" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N47" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>182</v>
@@ -3269,36 +3416,36 @@
         <v>183</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J48" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L48" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M48" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N48" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>65</v>
+        <v>258</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>185</v>
@@ -3336,107 +3483,107 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>66</v>
+        <v>259</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J50" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L50" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M50" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N50" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>67</v>
+        <v>260</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J51" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L51" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M51" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N51" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>68</v>
+        <v>261</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>182</v>
@@ -3445,86 +3592,86 @@
         <v>183</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J52" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L52" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M52" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N52" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
-        <v>46192</v>
+        <v>46197</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>69</v>
+        <v>262</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J53" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K53" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L53" s="4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M53" s="4">
-        <v>87</v>
+        <v>43.5</v>
       </c>
       <c r="N53" s="4">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
-        <v>46192</v>
+        <v>46197</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>70</v>
+        <v>263</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>182</v>
@@ -3533,36 +3680,36 @@
         <v>183</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J54" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K54" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L54" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M54" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N54" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
-        <v>46192</v>
+        <v>46197</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>71</v>
+        <v>264</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>181</v>
@@ -3583,36 +3730,36 @@
         <v>15</v>
       </c>
       <c r="J55" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55" s="4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L55" s="4">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M55" s="4">
-        <v>65.25</v>
+        <v>43.5</v>
       </c>
       <c r="N55" s="4">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
-        <v>46192</v>
+        <v>46197</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>72</v>
+        <v>265</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>182</v>
@@ -3621,36 +3768,36 @@
         <v>183</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J56" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L56" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M56" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N56" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>73</v>
+        <v>266</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>181</v>
@@ -3688,28 +3835,28 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>15</v>
@@ -3718,7 +3865,7 @@
         <v>1</v>
       </c>
       <c r="K58" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L58" s="4">
         <v>25</v>
@@ -3738,7 +3885,7 @@
         <v>18</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>181</v>
@@ -3759,19 +3906,19 @@
         <v>15</v>
       </c>
       <c r="J59" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K59" s="4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L59" s="4">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M59" s="4">
-        <v>65.25</v>
+        <v>21.75</v>
       </c>
       <c r="N59" s="4">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
@@ -3782,7 +3929,7 @@
         <v>18</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>181</v>
@@ -3803,19 +3950,19 @@
         <v>15</v>
       </c>
       <c r="J60" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K60" s="4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L60" s="4">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M60" s="4">
-        <v>65.25</v>
+        <v>21.75</v>
       </c>
       <c r="N60" s="4">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
@@ -3826,7 +3973,7 @@
         <v>18</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>181</v>
@@ -3870,7 +4017,7 @@
         <v>18</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>181</v>
@@ -3914,7 +4061,7 @@
         <v>18</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>181</v>
@@ -3955,16 +4102,16 @@
         <v>46192</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>182</v>
@@ -3973,7 +4120,7 @@
         <v>183</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>15</v>
@@ -3999,16 +4146,16 @@
         <v>46192</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>182</v>
@@ -4017,7 +4164,7 @@
         <v>183</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>15</v>
@@ -4043,43 +4190,43 @@
         <v>46192</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J66" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K66" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L66" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M66" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N66" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
@@ -4087,16 +4234,16 @@
         <v>46192</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>182</v>
@@ -4105,7 +4252,7 @@
         <v>183</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>15</v>
@@ -4131,16 +4278,16 @@
         <v>46192</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>182</v>
@@ -4149,7 +4296,7 @@
         <v>183</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>15</v>
@@ -4175,16 +4322,16 @@
         <v>46192</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>182</v>
@@ -4193,25 +4340,25 @@
         <v>183</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J69" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K69" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L69" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M69" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N69" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
@@ -4222,7 +4369,7 @@
         <v>18</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>181</v>
@@ -4263,25 +4410,25 @@
         <v>46192</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>15</v>
@@ -4290,7 +4437,7 @@
         <v>1</v>
       </c>
       <c r="K71" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L71" s="4">
         <v>25</v>
@@ -4307,16 +4454,16 @@
         <v>46192</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>182</v>
@@ -4325,25 +4472,25 @@
         <v>183</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J72" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K72" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L72" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M72" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N72" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
@@ -4351,25 +4498,25 @@
         <v>46192</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>15</v>
@@ -4378,7 +4525,7 @@
         <v>1</v>
       </c>
       <c r="K73" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L73" s="4">
         <v>25</v>
@@ -4398,7 +4545,7 @@
         <v>18</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>181</v>
@@ -4442,7 +4589,7 @@
         <v>18</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>181</v>
@@ -4486,7 +4633,7 @@
         <v>30</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>185</v>
@@ -4530,7 +4677,7 @@
         <v>30</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>185</v>
@@ -4571,16 +4718,16 @@
         <v>46192</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>182</v>
@@ -4589,7 +4736,7 @@
         <v>183</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>15</v>
@@ -4615,16 +4762,16 @@
         <v>46192</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>182</v>
@@ -4633,7 +4780,7 @@
         <v>183</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>15</v>
@@ -4659,16 +4806,16 @@
         <v>46192</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>182</v>
@@ -4677,7 +4824,7 @@
         <v>183</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>15</v>
@@ -4703,16 +4850,16 @@
         <v>46192</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>182</v>
@@ -4721,7 +4868,7 @@
         <v>183</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>15</v>
@@ -4747,25 +4894,25 @@
         <v>46192</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>15</v>
@@ -4774,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L82" s="4">
         <v>25</v>
@@ -4791,16 +4938,16 @@
         <v>46192</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>182</v>
@@ -4809,7 +4956,7 @@
         <v>183</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>15</v>
@@ -4838,7 +4985,7 @@
         <v>18</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>181</v>
@@ -4879,16 +5026,16 @@
         <v>46192</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>182</v>
@@ -4897,7 +5044,7 @@
         <v>183</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>15</v>
@@ -4923,25 +5070,25 @@
         <v>46192</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>15</v>
@@ -4950,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="K86" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L86" s="4">
         <v>25</v>
@@ -4970,7 +5117,7 @@
         <v>18</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>181</v>
@@ -5014,7 +5161,7 @@
         <v>18</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>181</v>
@@ -5055,98 +5202,98 @@
         <v>46192</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J89" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K89" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L89" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M89" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N89" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J90" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K90" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L90" s="4">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M90" s="4">
-        <v>65.25</v>
+        <v>21.75</v>
       </c>
       <c r="N90" s="4">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>185</v>
@@ -5184,72 +5331,72 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J92" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K92" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L92" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M92" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N92" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>15</v>
@@ -5258,7 +5405,7 @@
         <v>1</v>
       </c>
       <c r="K93" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L93" s="4">
         <v>25</v>
@@ -5272,13 +5419,13 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>185</v>
@@ -5316,19 +5463,19 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>182</v>
@@ -5337,7 +5484,7 @@
         <v>183</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>15</v>
@@ -5360,13 +5507,13 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>185</v>
@@ -5404,13 +5551,13 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>185</v>
@@ -5448,13 +5595,13 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>185</v>
@@ -5492,13 +5639,13 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>185</v>
@@ -5536,19 +5683,19 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>182</v>
@@ -5557,42 +5704,42 @@
         <v>183</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J100" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K100" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L100" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M100" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N100" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>182</v>
@@ -5601,7 +5748,7 @@
         <v>183</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>15</v>
@@ -5624,19 +5771,19 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>182</v>
@@ -5645,7 +5792,7 @@
         <v>183</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>15</v>
@@ -5668,13 +5815,13 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>185</v>
@@ -5712,13 +5859,13 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>181</v>
@@ -5756,19 +5903,19 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>182</v>
@@ -5777,7 +5924,7 @@
         <v>183</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>15</v>
@@ -5800,13 +5947,13 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>185</v>
@@ -5844,19 +5991,19 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>182</v>
@@ -5865,7 +6012,7 @@
         <v>183</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>15</v>
@@ -5888,28 +6035,28 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>15</v>
@@ -5918,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="K108" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L108" s="4">
         <v>25</v>
@@ -5932,19 +6079,19 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>182</v>
@@ -5953,7 +6100,7 @@
         <v>183</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>15</v>
@@ -5976,13 +6123,13 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>181</v>
@@ -6020,19 +6167,19 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>182</v>
@@ -6041,7 +6188,7 @@
         <v>183</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>15</v>
@@ -6064,19 +6211,19 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>182</v>
@@ -6085,7 +6232,7 @@
         <v>183</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>15</v>
@@ -6108,19 +6255,19 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>182</v>
@@ -6129,7 +6276,7 @@
         <v>183</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>15</v>
@@ -6152,19 +6299,19 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>182</v>
@@ -6173,7 +6320,7 @@
         <v>183</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>15</v>
@@ -6196,63 +6343,63 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J115" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K115" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L115" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M115" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N115" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>182</v>
@@ -6261,7 +6408,7 @@
         <v>183</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>15</v>
@@ -6284,13 +6431,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>181</v>
@@ -6328,13 +6475,13 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>181</v>
@@ -6372,19 +6519,19 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>182</v>
@@ -6393,7 +6540,7 @@
         <v>183</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
@@ -6416,13 +6563,13 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>181</v>
@@ -6460,13 +6607,13 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>181</v>
@@ -6504,13 +6651,13 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>181</v>
@@ -6548,13 +6695,13 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>181</v>
@@ -6575,45 +6722,45 @@
         <v>15</v>
       </c>
       <c r="J123" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K123" s="4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L123" s="4">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M123" s="4">
-        <v>65.25</v>
+        <v>21.75</v>
       </c>
       <c r="N123" s="4">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
@@ -6622,7 +6769,7 @@
         <v>1</v>
       </c>
       <c r="K124" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L124" s="4">
         <v>25</v>
@@ -6639,16 +6786,16 @@
         <v>46193</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>182</v>
@@ -6657,25 +6804,25 @@
         <v>183</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J125" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K125" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L125" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M125" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N125" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.3">
@@ -6683,25 +6830,25 @@
         <v>46193</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
@@ -6710,7 +6857,7 @@
         <v>1</v>
       </c>
       <c r="K126" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L126" s="4">
         <v>25</v>
@@ -6727,16 +6874,16 @@
         <v>46193</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>182</v>
@@ -6745,7 +6892,7 @@
         <v>183</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
@@ -6774,7 +6921,7 @@
         <v>18</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>181</v>
@@ -6795,19 +6942,19 @@
         <v>15</v>
       </c>
       <c r="J128" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K128" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L128" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M128" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N128" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
@@ -6815,16 +6962,16 @@
         <v>46193</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>182</v>
@@ -6833,7 +6980,7 @@
         <v>183</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>15</v>
@@ -6859,16 +7006,16 @@
         <v>46193</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>182</v>
@@ -6877,7 +7024,7 @@
         <v>183</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
@@ -6906,7 +7053,7 @@
         <v>30</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>185</v>
@@ -6947,25 +7094,25 @@
         <v>46193</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>15</v>
@@ -6974,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="K132" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L132" s="4">
         <v>25</v>
@@ -6991,25 +7138,25 @@
         <v>46193</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
@@ -7018,7 +7165,7 @@
         <v>1</v>
       </c>
       <c r="K133" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L133" s="4">
         <v>25</v>
@@ -7035,16 +7182,16 @@
         <v>46193</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>182</v>
@@ -7053,25 +7200,25 @@
         <v>183</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J134" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K134" s="4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L134" s="4">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M134" s="4">
-        <v>65.25</v>
+        <v>21.75</v>
       </c>
       <c r="N134" s="4">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.3">
@@ -7079,16 +7226,16 @@
         <v>46193</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>182</v>
@@ -7097,7 +7244,7 @@
         <v>183</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
@@ -7126,7 +7273,7 @@
         <v>18</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>181</v>
@@ -7170,7 +7317,7 @@
         <v>18</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>181</v>
@@ -7211,16 +7358,16 @@
         <v>46193</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>182</v>
@@ -7229,25 +7376,25 @@
         <v>183</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J138" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K138" s="4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L138" s="4">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M138" s="4">
-        <v>65.25</v>
+        <v>21.75</v>
       </c>
       <c r="N138" s="4">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.3">
@@ -7255,43 +7402,43 @@
         <v>46193</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>187</v>
+        <v>32</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J139" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K139" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L139" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M139" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N139" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.3">
@@ -7302,7 +7449,7 @@
         <v>18</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>181</v>
@@ -7343,16 +7490,16 @@
         <v>46193</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>182</v>
@@ -7361,7 +7508,7 @@
         <v>183</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>15</v>
@@ -7390,7 +7537,7 @@
         <v>18</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>181</v>
@@ -7431,16 +7578,16 @@
         <v>46193</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>182</v>
@@ -7449,7 +7596,7 @@
         <v>183</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>15</v>
@@ -7478,7 +7625,7 @@
         <v>18</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>181</v>
@@ -7522,7 +7669,7 @@
         <v>18</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>181</v>
@@ -7543,19 +7690,19 @@
         <v>15</v>
       </c>
       <c r="J145" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K145" s="4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L145" s="4">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M145" s="4">
-        <v>65.25</v>
+        <v>21.75</v>
       </c>
       <c r="N145" s="4">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
@@ -7566,7 +7713,7 @@
         <v>18</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>181</v>
@@ -7607,16 +7754,16 @@
         <v>46193</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>182</v>
@@ -7625,7 +7772,7 @@
         <v>183</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>15</v>
@@ -7654,7 +7801,7 @@
         <v>18</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>181</v>
@@ -7698,7 +7845,7 @@
         <v>18</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>181</v>
@@ -7739,16 +7886,16 @@
         <v>46193</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>182</v>
@@ -7757,25 +7904,25 @@
         <v>183</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J150" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K150" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L150" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M150" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N150" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
@@ -7786,7 +7933,7 @@
         <v>18</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>181</v>
@@ -7807,19 +7954,19 @@
         <v>15</v>
       </c>
       <c r="J151" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K151" s="4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L151" s="4">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M151" s="4">
-        <v>65.25</v>
+        <v>21.75</v>
       </c>
       <c r="N151" s="4">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
@@ -7830,7 +7977,7 @@
         <v>18</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>181</v>
@@ -7851,19 +7998,19 @@
         <v>15</v>
       </c>
       <c r="J152" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K152" s="4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L152" s="4">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M152" s="4">
-        <v>65.25</v>
+        <v>21.75</v>
       </c>
       <c r="N152" s="4">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
@@ -7874,7 +8021,7 @@
         <v>18</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>181</v>
@@ -7915,43 +8062,43 @@
         <v>46193</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J154" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K154" s="4">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L154" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M154" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N154" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
@@ -7962,7 +8109,7 @@
         <v>18</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>181</v>
@@ -7983,19 +8130,19 @@
         <v>15</v>
       </c>
       <c r="J155" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K155" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L155" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M155" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N155" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.3">
@@ -8006,7 +8153,7 @@
         <v>18</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>181</v>
@@ -8050,7 +8197,7 @@
         <v>18</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>181</v>
@@ -8071,19 +8218,19 @@
         <v>15</v>
       </c>
       <c r="J157" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K157" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L157" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M157" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N157" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
@@ -8091,43 +8238,43 @@
         <v>46193</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J158" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K158" s="4">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L158" s="4">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="M158" s="4">
-        <v>130.5</v>
+        <v>21.75</v>
       </c>
       <c r="N158" s="4">
-        <v>4.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
@@ -8135,25 +8282,25 @@
         <v>46193</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>15</v>
@@ -8162,7 +8309,7 @@
         <v>1</v>
       </c>
       <c r="K159" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L159" s="4">
         <v>25</v>
@@ -8179,25 +8326,25 @@
         <v>46193</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>15</v>
@@ -8206,7 +8353,7 @@
         <v>1</v>
       </c>
       <c r="K160" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L160" s="4">
         <v>25</v>
@@ -8220,28 +8367,28 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="I161" s="3" t="s">
         <v>15</v>
@@ -8250,7 +8397,7 @@
         <v>1</v>
       </c>
       <c r="K161" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L161" s="4">
         <v>25</v>
@@ -8264,19 +8411,19 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>194</v>
+        <v>151</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>182</v>
@@ -8285,7 +8432,7 @@
         <v>183</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I162" s="3" t="s">
         <v>15</v>
@@ -8308,19 +8455,19 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>182</v>
@@ -8329,7 +8476,7 @@
         <v>183</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I163" s="3" t="s">
         <v>15</v>
@@ -8352,19 +8499,19 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>182</v>
@@ -8373,51 +8520,51 @@
         <v>183</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I164" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J164" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K164" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L164" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M164" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N164" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I165" s="3" t="s">
         <v>15</v>
@@ -8426,7 +8573,7 @@
         <v>1</v>
       </c>
       <c r="K165" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L165" s="4">
         <v>25</v>
@@ -8440,13 +8587,13 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>181</v>
@@ -8484,13 +8631,13 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>181</v>
@@ -8511,30 +8658,30 @@
         <v>15</v>
       </c>
       <c r="J167" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K167" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L167" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M167" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N167" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>181</v>
@@ -8572,19 +8719,19 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>182</v>
@@ -8593,36 +8740,36 @@
         <v>183</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I169" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J169" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K169" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L169" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M169" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N169" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>181</v>
@@ -8643,30 +8790,30 @@
         <v>15</v>
       </c>
       <c r="J170" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K170" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L170" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M170" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N170" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>181</v>
@@ -8704,19 +8851,19 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>182</v>
@@ -8725,7 +8872,7 @@
         <v>183</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I172" s="3" t="s">
         <v>15</v>
@@ -8748,19 +8895,19 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>182</v>
@@ -8769,7 +8916,7 @@
         <v>183</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I173" s="3" t="s">
         <v>15</v>
@@ -8792,13 +8939,13 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>181</v>
@@ -8836,28 +8983,28 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I175" s="3" t="s">
         <v>15</v>
@@ -8866,7 +9013,7 @@
         <v>1</v>
       </c>
       <c r="K175" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L175" s="4">
         <v>25</v>
@@ -8880,28 +9027,28 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I176" s="3" t="s">
         <v>15</v>
@@ -8910,7 +9057,7 @@
         <v>1</v>
       </c>
       <c r="K176" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L176" s="4">
         <v>25</v>
@@ -8924,19 +9071,19 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>182</v>
@@ -8945,25 +9092,25 @@
         <v>183</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I177" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J177" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K177" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L177" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M177" s="4">
-        <v>43.5</v>
+        <v>21.75</v>
       </c>
       <c r="N177" s="4">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.3">
@@ -8974,7 +9121,7 @@
         <v>30</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>185</v>
@@ -9018,7 +9165,7 @@
         <v>30</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>185</v>
@@ -9059,16 +9206,16 @@
         <v>46196</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>182</v>
@@ -9077,7 +9224,7 @@
         <v>183</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I180" s="3" t="s">
         <v>15</v>
@@ -9103,25 +9250,25 @@
         <v>46196</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I181" s="3" t="s">
         <v>15</v>
@@ -9130,7 +9277,7 @@
         <v>1</v>
       </c>
       <c r="K181" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L181" s="4">
         <v>25</v>
@@ -9147,16 +9294,16 @@
         <v>46196</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>182</v>
@@ -9165,7 +9312,7 @@
         <v>183</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I182" s="3" t="s">
         <v>15</v>
@@ -9194,7 +9341,7 @@
         <v>18</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>181</v>
@@ -9238,7 +9385,7 @@
         <v>18</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>181</v>
@@ -9279,16 +9426,16 @@
         <v>46196</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>182</v>
@@ -9297,7 +9444,7 @@
         <v>183</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>15</v>
@@ -9323,16 +9470,16 @@
         <v>46196</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>182</v>
@@ -9341,25 +9488,25 @@
         <v>183</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J186" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K186" s="4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L186" s="4">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="M186" s="4">
-        <v>65.25</v>
+        <v>21.75</v>
       </c>
       <c r="N186" s="4">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.3">
@@ -9370,39 +9517,2195 @@
         <v>18</v>
       </c>
       <c r="C187" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H187" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I187" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J187" s="4">
+        <v>1</v>
+      </c>
+      <c r="K187" s="4">
+        <v>6</v>
+      </c>
+      <c r="L187" s="4">
+        <v>25</v>
+      </c>
+      <c r="M187" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N187" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A188" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H188" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I188" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J188" s="4">
+        <v>1</v>
+      </c>
+      <c r="K188" s="4">
+        <v>4</v>
+      </c>
+      <c r="L188" s="4">
+        <v>25</v>
+      </c>
+      <c r="M188" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N188" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A189" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J189" s="4">
+        <v>1</v>
+      </c>
+      <c r="K189" s="4">
+        <v>6</v>
+      </c>
+      <c r="L189" s="4">
+        <v>25</v>
+      </c>
+      <c r="M189" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N189" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A190" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J190" s="4">
+        <v>1</v>
+      </c>
+      <c r="K190" s="4">
+        <v>6</v>
+      </c>
+      <c r="L190" s="4">
+        <v>25</v>
+      </c>
+      <c r="M190" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N190" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A191" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H191" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I191" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J191" s="4">
+        <v>1</v>
+      </c>
+      <c r="K191" s="4">
+        <v>6</v>
+      </c>
+      <c r="L191" s="4">
+        <v>25</v>
+      </c>
+      <c r="M191" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N191" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A192" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J192" s="4">
+        <v>1</v>
+      </c>
+      <c r="K192" s="4">
+        <v>6</v>
+      </c>
+      <c r="L192" s="4">
+        <v>25</v>
+      </c>
+      <c r="M192" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N192" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A193" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J193" s="4">
+        <v>1</v>
+      </c>
+      <c r="K193" s="4">
+        <v>6</v>
+      </c>
+      <c r="L193" s="4">
+        <v>25</v>
+      </c>
+      <c r="M193" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N193" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A194" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H194" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I194" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J194" s="4">
+        <v>1</v>
+      </c>
+      <c r="K194" s="4">
+        <v>6</v>
+      </c>
+      <c r="L194" s="4">
+        <v>25</v>
+      </c>
+      <c r="M194" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N194" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A195" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H195" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I195" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J195" s="4">
+        <v>1</v>
+      </c>
+      <c r="K195" s="4">
+        <v>6</v>
+      </c>
+      <c r="L195" s="4">
+        <v>25</v>
+      </c>
+      <c r="M195" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N195" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A196" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H196" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J196" s="4">
+        <v>1</v>
+      </c>
+      <c r="K196" s="4">
+        <v>6</v>
+      </c>
+      <c r="L196" s="4">
+        <v>25</v>
+      </c>
+      <c r="M196" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N196" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A197" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H197" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J197" s="4">
+        <v>1</v>
+      </c>
+      <c r="K197" s="4">
+        <v>6</v>
+      </c>
+      <c r="L197" s="4">
+        <v>25</v>
+      </c>
+      <c r="M197" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N197" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A198" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C198" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D187" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E187" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H187" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I187" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J187" s="4">
-        <v>1</v>
-      </c>
-      <c r="K187" s="4">
-        <v>6</v>
-      </c>
-      <c r="L187" s="4">
-        <v>25</v>
-      </c>
-      <c r="M187" s="4">
-        <v>21.75</v>
-      </c>
-      <c r="N187" s="4">
+      <c r="D198" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H198" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J198" s="4">
+        <v>1</v>
+      </c>
+      <c r="K198" s="4">
+        <v>6</v>
+      </c>
+      <c r="L198" s="4">
+        <v>25</v>
+      </c>
+      <c r="M198" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N198" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A199" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H199" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I199" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J199" s="4">
+        <v>1</v>
+      </c>
+      <c r="K199" s="4">
+        <v>6</v>
+      </c>
+      <c r="L199" s="4">
+        <v>25</v>
+      </c>
+      <c r="M199" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N199" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A200" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H200" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I200" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J200" s="4">
+        <v>1</v>
+      </c>
+      <c r="K200" s="4">
+        <v>6</v>
+      </c>
+      <c r="L200" s="4">
+        <v>25</v>
+      </c>
+      <c r="M200" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N200" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A201" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H201" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J201" s="4">
+        <v>1</v>
+      </c>
+      <c r="K201" s="4">
+        <v>6</v>
+      </c>
+      <c r="L201" s="4">
+        <v>25</v>
+      </c>
+      <c r="M201" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N201" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A202" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H202" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I202" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J202" s="4">
+        <v>1</v>
+      </c>
+      <c r="K202" s="4">
+        <v>6</v>
+      </c>
+      <c r="L202" s="4">
+        <v>25</v>
+      </c>
+      <c r="M202" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N202" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A203" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H203" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I203" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J203" s="4">
+        <v>1</v>
+      </c>
+      <c r="K203" s="4">
+        <v>6</v>
+      </c>
+      <c r="L203" s="4">
+        <v>25</v>
+      </c>
+      <c r="M203" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N203" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A204" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H204" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I204" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J204" s="4">
+        <v>1</v>
+      </c>
+      <c r="K204" s="4">
+        <v>6</v>
+      </c>
+      <c r="L204" s="4">
+        <v>25</v>
+      </c>
+      <c r="M204" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N204" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A205" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H205" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J205" s="4">
+        <v>1</v>
+      </c>
+      <c r="K205" s="4">
+        <v>4</v>
+      </c>
+      <c r="L205" s="4">
+        <v>25</v>
+      </c>
+      <c r="M205" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N205" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A206" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H206" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I206" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J206" s="4">
+        <v>1</v>
+      </c>
+      <c r="K206" s="4">
+        <v>4</v>
+      </c>
+      <c r="L206" s="4">
+        <v>25</v>
+      </c>
+      <c r="M206" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N206" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A207" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H207" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I207" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J207" s="4">
+        <v>1</v>
+      </c>
+      <c r="K207" s="4">
+        <v>4</v>
+      </c>
+      <c r="L207" s="4">
+        <v>25</v>
+      </c>
+      <c r="M207" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N207" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A208" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H208" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J208" s="4">
+        <v>1</v>
+      </c>
+      <c r="K208" s="4">
+        <v>6</v>
+      </c>
+      <c r="L208" s="4">
+        <v>25</v>
+      </c>
+      <c r="M208" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N208" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A209" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H209" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I209" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J209" s="4">
+        <v>1</v>
+      </c>
+      <c r="K209" s="4">
+        <v>6</v>
+      </c>
+      <c r="L209" s="4">
+        <v>25</v>
+      </c>
+      <c r="M209" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N209" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A210" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H210" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J210" s="4">
+        <v>1</v>
+      </c>
+      <c r="K210" s="4">
+        <v>6</v>
+      </c>
+      <c r="L210" s="4">
+        <v>25</v>
+      </c>
+      <c r="M210" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N210" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A211" s="5">
+        <v>46196</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H211" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J211" s="4">
+        <v>1</v>
+      </c>
+      <c r="K211" s="4">
+        <v>6</v>
+      </c>
+      <c r="L211" s="4">
+        <v>25</v>
+      </c>
+      <c r="M211" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N211" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A212" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H212" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J212" s="4">
+        <v>1</v>
+      </c>
+      <c r="K212" s="4">
+        <v>6</v>
+      </c>
+      <c r="L212" s="4">
+        <v>25</v>
+      </c>
+      <c r="M212" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N212" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A213" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H213" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J213" s="4">
+        <v>1</v>
+      </c>
+      <c r="K213" s="4">
+        <v>6</v>
+      </c>
+      <c r="L213" s="4">
+        <v>25</v>
+      </c>
+      <c r="M213" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N213" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A214" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J214" s="4">
+        <v>1</v>
+      </c>
+      <c r="K214" s="4">
+        <v>6</v>
+      </c>
+      <c r="L214" s="4">
+        <v>25</v>
+      </c>
+      <c r="M214" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N214" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A215" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J215" s="4">
+        <v>1</v>
+      </c>
+      <c r="K215" s="4">
+        <v>6</v>
+      </c>
+      <c r="L215" s="4">
+        <v>25</v>
+      </c>
+      <c r="M215" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N215" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A216" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J216" s="4">
+        <v>1</v>
+      </c>
+      <c r="K216" s="4">
+        <v>4</v>
+      </c>
+      <c r="L216" s="4">
+        <v>25</v>
+      </c>
+      <c r="M216" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N216" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A217" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H217" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J217" s="4">
+        <v>1</v>
+      </c>
+      <c r="K217" s="4">
+        <v>4</v>
+      </c>
+      <c r="L217" s="4">
+        <v>25</v>
+      </c>
+      <c r="M217" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N217" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A218" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H218" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I218" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J218" s="4">
+        <v>1</v>
+      </c>
+      <c r="K218" s="4">
+        <v>6</v>
+      </c>
+      <c r="L218" s="4">
+        <v>25</v>
+      </c>
+      <c r="M218" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N218" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A219" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H219" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J219" s="4">
+        <v>1</v>
+      </c>
+      <c r="K219" s="4">
+        <v>6</v>
+      </c>
+      <c r="L219" s="4">
+        <v>25</v>
+      </c>
+      <c r="M219" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N219" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A220" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H220" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I220" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J220" s="4">
+        <v>1</v>
+      </c>
+      <c r="K220" s="4">
+        <v>6</v>
+      </c>
+      <c r="L220" s="4">
+        <v>25</v>
+      </c>
+      <c r="M220" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N220" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A221" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H221" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J221" s="4">
+        <v>1</v>
+      </c>
+      <c r="K221" s="4">
+        <v>6</v>
+      </c>
+      <c r="L221" s="4">
+        <v>25</v>
+      </c>
+      <c r="M221" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N221" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A222" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H222" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J222" s="4">
+        <v>1</v>
+      </c>
+      <c r="K222" s="4">
+        <v>6</v>
+      </c>
+      <c r="L222" s="4">
+        <v>25</v>
+      </c>
+      <c r="M222" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N222" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A223" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H223" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J223" s="4">
+        <v>1</v>
+      </c>
+      <c r="K223" s="4">
+        <v>6</v>
+      </c>
+      <c r="L223" s="4">
+        <v>25</v>
+      </c>
+      <c r="M223" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N223" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A224" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H224" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J224" s="4">
+        <v>1</v>
+      </c>
+      <c r="K224" s="4">
+        <v>6</v>
+      </c>
+      <c r="L224" s="4">
+        <v>25</v>
+      </c>
+      <c r="M224" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N224" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A225" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J225" s="4">
+        <v>1</v>
+      </c>
+      <c r="K225" s="4">
+        <v>4</v>
+      </c>
+      <c r="L225" s="4">
+        <v>25</v>
+      </c>
+      <c r="M225" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N225" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A226" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H226" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I226" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J226" s="4">
+        <v>1</v>
+      </c>
+      <c r="K226" s="4">
+        <v>6</v>
+      </c>
+      <c r="L226" s="4">
+        <v>25</v>
+      </c>
+      <c r="M226" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N226" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A227" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J227" s="4">
+        <v>1</v>
+      </c>
+      <c r="K227" s="4">
+        <v>6</v>
+      </c>
+      <c r="L227" s="4">
+        <v>25</v>
+      </c>
+      <c r="M227" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N227" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A228" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H228" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J228" s="4">
+        <v>1</v>
+      </c>
+      <c r="K228" s="4">
+        <v>4</v>
+      </c>
+      <c r="L228" s="4">
+        <v>25</v>
+      </c>
+      <c r="M228" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N228" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A229" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H229" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J229" s="4">
+        <v>1</v>
+      </c>
+      <c r="K229" s="4">
+        <v>4</v>
+      </c>
+      <c r="L229" s="4">
+        <v>25</v>
+      </c>
+      <c r="M229" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N229" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A230" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H230" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J230" s="4">
+        <v>1</v>
+      </c>
+      <c r="K230" s="4">
+        <v>6</v>
+      </c>
+      <c r="L230" s="4">
+        <v>25</v>
+      </c>
+      <c r="M230" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N230" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A231" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H231" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J231" s="4">
+        <v>1</v>
+      </c>
+      <c r="K231" s="4">
+        <v>6</v>
+      </c>
+      <c r="L231" s="4">
+        <v>25</v>
+      </c>
+      <c r="M231" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N231" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A232" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H232" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J232" s="4">
+        <v>1</v>
+      </c>
+      <c r="K232" s="4">
+        <v>4</v>
+      </c>
+      <c r="L232" s="4">
+        <v>25</v>
+      </c>
+      <c r="M232" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N232" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A233" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J233" s="4">
+        <v>1</v>
+      </c>
+      <c r="K233" s="4">
+        <v>6</v>
+      </c>
+      <c r="L233" s="4">
+        <v>25</v>
+      </c>
+      <c r="M233" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N233" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A234" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J234" s="4">
+        <v>1</v>
+      </c>
+      <c r="K234" s="4">
+        <v>6</v>
+      </c>
+      <c r="L234" s="4">
+        <v>25</v>
+      </c>
+      <c r="M234" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N234" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A235" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H235" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J235" s="4">
+        <v>1</v>
+      </c>
+      <c r="K235" s="4">
+        <v>6</v>
+      </c>
+      <c r="L235" s="4">
+        <v>25</v>
+      </c>
+      <c r="M235" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N235" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A236" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H236" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J236" s="4">
+        <v>1</v>
+      </c>
+      <c r="K236" s="4">
+        <v>6</v>
+      </c>
+      <c r="L236" s="4">
+        <v>25</v>
+      </c>
+      <c r="M236" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N236" s="4">
         <v>0.75</v>
       </c>
     </row>

--- a/data/BD Campaña San Juan.xlsx
+++ b/data/BD Campaña San Juan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jescalera\Documents\SAN JUAN DASHBOARD\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E97168-AB68-4A91-8326-04D8B5114E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AC8157-7AF4-467B-9DE4-40924A0F490C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{195A31B7-CEAF-4C8B-96A9-10FB87544323}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Base" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$N$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$N$271</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="300">
   <si>
     <t>Fecha</t>
   </si>
@@ -847,6 +847,99 @@
   </si>
   <si>
     <t>003499</t>
+  </si>
+  <si>
+    <t>003502</t>
+  </si>
+  <si>
+    <t>003507</t>
+  </si>
+  <si>
+    <t>003512</t>
+  </si>
+  <si>
+    <t>003521</t>
+  </si>
+  <si>
+    <t>000559</t>
+  </si>
+  <si>
+    <t>000560</t>
+  </si>
+  <si>
+    <t>000561</t>
+  </si>
+  <si>
+    <t>000562</t>
+  </si>
+  <si>
+    <t>003542</t>
+  </si>
+  <si>
+    <t>003543</t>
+  </si>
+  <si>
+    <t>003544</t>
+  </si>
+  <si>
+    <t>003546</t>
+  </si>
+  <si>
+    <t>003551</t>
+  </si>
+  <si>
+    <t>003554</t>
+  </si>
+  <si>
+    <t>003267</t>
+  </si>
+  <si>
+    <t>063124</t>
+  </si>
+  <si>
+    <t>063125</t>
+  </si>
+  <si>
+    <t>063126</t>
+  </si>
+  <si>
+    <t>003273</t>
+  </si>
+  <si>
+    <t>063130</t>
+  </si>
+  <si>
+    <t>063131</t>
+  </si>
+  <si>
+    <t>003284</t>
+  </si>
+  <si>
+    <t>003290</t>
+  </si>
+  <si>
+    <t>003299</t>
+  </si>
+  <si>
+    <t>003305</t>
+  </si>
+  <si>
+    <t>003308</t>
+  </si>
+  <si>
+    <t>003324</t>
+  </si>
+  <si>
+    <t>003325</t>
+  </si>
+  <si>
+    <t>003329</t>
+  </si>
+  <si>
+    <t>003341</t>
+  </si>
+  <si>
+    <t>003348</t>
   </si>
 </sst>
 </file>
@@ -993,10 +1086,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10374E95-5D2C-4793-97BF-BE592FBD4129}" name="BD" displayName="BD" ref="A1:N236" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:N236" xr:uid="{96A8FB89-0BFB-4212-8B86-7443EF4F1B7D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N236">
-    <sortCondition descending="1" ref="J1:J236"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10374E95-5D2C-4793-97BF-BE592FBD4129}" name="BD" displayName="BD" ref="A1:N271" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N271" xr:uid="{96A8FB89-0BFB-4212-8B86-7443EF4F1B7D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N271">
+    <sortCondition descending="1" ref="J1:J271"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{E0617225-4DD1-4A0C-B351-A45F4B1AF696}" name="Fecha" dataDxfId="13"/>
@@ -1315,7 +1408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A8FB89-0BFB-4212-8B86-7443EF4F1B7D}">
-  <dimension ref="A1:N236"/>
+  <dimension ref="A1:N271"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
@@ -1459,13 +1552,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>69</v>
+        <v>276</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>177</v>
@@ -1486,19 +1579,19 @@
         <v>15</v>
       </c>
       <c r="J4" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" s="4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L4" s="4">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M4" s="4">
-        <v>87</v>
+        <v>108.75</v>
       </c>
       <c r="N4" s="4">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -1506,43 +1599,43 @@
         <v>46192</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J5" s="4">
+        <v>4</v>
+      </c>
+      <c r="K5" s="4">
+        <v>16</v>
+      </c>
+      <c r="L5" s="4">
+        <v>100</v>
+      </c>
+      <c r="M5" s="4">
+        <v>87</v>
+      </c>
+      <c r="N5" s="4">
         <v>3</v>
-      </c>
-      <c r="K5" s="4">
-        <v>18</v>
-      </c>
-      <c r="L5" s="4">
-        <v>75</v>
-      </c>
-      <c r="M5" s="4">
-        <v>65.25</v>
-      </c>
-      <c r="N5" s="4">
-        <v>2.25</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1553,7 +1646,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>181</v>
@@ -1597,7 +1690,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>181</v>
@@ -1641,7 +1734,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>181</v>
@@ -1685,7 +1778,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>181</v>
@@ -1729,7 +1822,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>181</v>
@@ -1773,7 +1866,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>181</v>
@@ -1811,28 +1904,28 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>15</v>
@@ -1841,7 +1934,7 @@
         <v>3</v>
       </c>
       <c r="K12" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L12" s="4">
         <v>75</v>
@@ -1858,25 +1951,25 @@
         <v>46193</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>15</v>
@@ -1885,7 +1978,7 @@
         <v>3</v>
       </c>
       <c r="K13" s="4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L13" s="4">
         <v>75</v>
@@ -1905,7 +1998,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>181</v>
@@ -1949,7 +2042,7 @@
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>181</v>
@@ -1993,7 +2086,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>181</v>
@@ -2037,7 +2130,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>181</v>
@@ -2081,7 +2174,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>181</v>
@@ -2119,13 +2212,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>218</v>
+        <v>168</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>181</v>
@@ -2163,19 +2256,19 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>182</v>
@@ -2184,7 +2277,7 @@
         <v>183</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>15</v>
@@ -2207,19 +2300,19 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>182</v>
@@ -2228,7 +2321,7 @@
         <v>183</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>15</v>
@@ -2251,57 +2344,57 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>14</v>
+        <v>268</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J22" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="4">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L22" s="4">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M22" s="4">
-        <v>43.5</v>
+        <v>65.25</v>
       </c>
       <c r="N22" s="4">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>21</v>
+        <v>278</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>181</v>
@@ -2322,30 +2415,30 @@
         <v>15</v>
       </c>
       <c r="J23" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L23" s="4">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M23" s="4">
-        <v>43.5</v>
+        <v>65.25</v>
       </c>
       <c r="N23" s="4">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>25</v>
+        <v>279</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>181</v>
@@ -2366,45 +2459,45 @@
         <v>15</v>
       </c>
       <c r="J24" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" s="4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L24" s="4">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M24" s="4">
-        <v>43.5</v>
+        <v>65.25</v>
       </c>
       <c r="N24" s="4">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>15</v>
@@ -2413,7 +2506,7 @@
         <v>2</v>
       </c>
       <c r="K25" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L25" s="4">
         <v>50</v>
@@ -2430,16 +2523,16 @@
         <v>46192</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>182</v>
@@ -2448,7 +2541,7 @@
         <v>183</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>15</v>
@@ -2477,7 +2570,7 @@
         <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>181</v>
@@ -2518,16 +2611,16 @@
         <v>46192</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>182</v>
@@ -2536,7 +2629,7 @@
         <v>183</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>15</v>
@@ -2562,16 +2655,16 @@
         <v>46192</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>182</v>
@@ -2580,7 +2673,7 @@
         <v>183</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>15</v>
@@ -2606,25 +2699,25 @@
         <v>46192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>15</v>
@@ -2633,7 +2726,7 @@
         <v>2</v>
       </c>
       <c r="K30" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L30" s="4">
         <v>50</v>
@@ -2650,16 +2743,16 @@
         <v>46192</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>182</v>
@@ -2668,7 +2761,7 @@
         <v>183</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>15</v>
@@ -2697,7 +2790,7 @@
         <v>18</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>181</v>
@@ -2741,7 +2834,7 @@
         <v>13</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>177</v>
@@ -2779,28 +2872,28 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>15</v>
@@ -2809,7 +2902,7 @@
         <v>2</v>
       </c>
       <c r="K34" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L34" s="4">
         <v>50</v>
@@ -2823,19 +2916,19 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>182</v>
@@ -2844,7 +2937,7 @@
         <v>183</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>15</v>
@@ -2867,13 +2960,13 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>177</v>
@@ -2914,25 +3007,25 @@
         <v>46193</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>15</v>
@@ -2941,7 +3034,7 @@
         <v>2</v>
       </c>
       <c r="K37" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L37" s="4">
         <v>50</v>
@@ -2958,16 +3051,16 @@
         <v>46193</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>182</v>
@@ -2976,7 +3069,7 @@
         <v>183</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>15</v>
@@ -3005,13 +3098,13 @@
         <v>13</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>178</v>
@@ -3020,7 +3113,7 @@
         <v>179</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>15</v>
@@ -3049,7 +3142,7 @@
         <v>18</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>181</v>
@@ -3093,7 +3186,7 @@
         <v>18</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>181</v>
@@ -3134,25 +3227,25 @@
         <v>46193</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>15</v>
@@ -3161,7 +3254,7 @@
         <v>2</v>
       </c>
       <c r="K42" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L42" s="4">
         <v>50</v>
@@ -3181,7 +3274,7 @@
         <v>18</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>181</v>
@@ -3219,19 +3312,19 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>182</v>
@@ -3240,7 +3333,7 @@
         <v>183</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>15</v>
@@ -3263,13 +3356,13 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>181</v>
@@ -3307,19 +3400,19 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>182</v>
@@ -3328,7 +3421,7 @@
         <v>183</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>15</v>
@@ -3354,16 +3447,16 @@
         <v>46196</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>182</v>
@@ -3372,7 +3465,7 @@
         <v>183</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>15</v>
@@ -3398,16 +3491,16 @@
         <v>46196</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>182</v>
@@ -3416,7 +3509,7 @@
         <v>183</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>15</v>
@@ -3445,7 +3538,7 @@
         <v>30</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>185</v>
@@ -3486,25 +3579,25 @@
         <v>46196</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>15</v>
@@ -3513,7 +3606,7 @@
         <v>2</v>
       </c>
       <c r="K50" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L50" s="4">
         <v>50</v>
@@ -3530,25 +3623,25 @@
         <v>46196</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>15</v>
@@ -3557,7 +3650,7 @@
         <v>2</v>
       </c>
       <c r="K51" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L51" s="4">
         <v>50</v>
@@ -3574,16 +3667,16 @@
         <v>46196</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>182</v>
@@ -3592,7 +3685,7 @@
         <v>183</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>15</v>
@@ -3615,28 +3708,28 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>15</v>
@@ -3645,7 +3738,7 @@
         <v>2</v>
       </c>
       <c r="K53" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L53" s="4">
         <v>50</v>
@@ -3659,28 +3752,28 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>15</v>
@@ -3689,7 +3782,7 @@
         <v>2</v>
       </c>
       <c r="K54" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L54" s="4">
         <v>50</v>
@@ -3703,13 +3796,13 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>181</v>
@@ -3753,7 +3846,7 @@
         <v>18</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>181</v>
@@ -3791,13 +3884,13 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>181</v>
@@ -3835,57 +3928,57 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
-        <v>46191</v>
+        <v>46197</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J58" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" s="4">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L58" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M58" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N58" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
-        <v>46192</v>
+        <v>46197</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>181</v>
@@ -3906,30 +3999,30 @@
         <v>15</v>
       </c>
       <c r="J59" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L59" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M59" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N59" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>22</v>
+        <v>266</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>181</v>
@@ -3950,30 +4043,30 @@
         <v>15</v>
       </c>
       <c r="J60" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L60" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M60" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N60" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>23</v>
+        <v>280</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>181</v>
@@ -3994,30 +4087,30 @@
         <v>15</v>
       </c>
       <c r="J61" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K61" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L61" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M61" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N61" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>181</v>
@@ -4038,30 +4131,30 @@
         <v>15</v>
       </c>
       <c r="J62" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K62" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L62" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M62" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N62" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>28</v>
+        <v>292</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>181</v>
@@ -4082,30 +4175,30 @@
         <v>15</v>
       </c>
       <c r="J63" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L63" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M63" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N63" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
-        <v>46192</v>
+        <v>46198</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>29</v>
+        <v>298</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>181</v>
@@ -4126,45 +4219,45 @@
         <v>15</v>
       </c>
       <c r="J64" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L64" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M64" s="4">
-        <v>21.75</v>
+        <v>43.5</v>
       </c>
       <c r="N64" s="4">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>15</v>
@@ -4173,7 +4266,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L65" s="4">
         <v>25</v>
@@ -4193,7 +4286,7 @@
         <v>18</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>181</v>
@@ -4237,7 +4330,7 @@
         <v>18</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>181</v>
@@ -4281,7 +4374,7 @@
         <v>18</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>181</v>
@@ -4322,16 +4415,16 @@
         <v>46192</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>182</v>
@@ -4340,7 +4433,7 @@
         <v>183</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>15</v>
@@ -4369,7 +4462,7 @@
         <v>18</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>181</v>
@@ -4410,16 +4503,16 @@
         <v>46192</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>182</v>
@@ -4428,7 +4521,7 @@
         <v>183</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>15</v>
@@ -4457,7 +4550,7 @@
         <v>30</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>185</v>
@@ -4498,25 +4591,25 @@
         <v>46192</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>15</v>
@@ -4525,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="K73" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L73" s="4">
         <v>25</v>
@@ -4545,7 +4638,7 @@
         <v>18</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>181</v>
@@ -4589,7 +4682,7 @@
         <v>18</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>181</v>
@@ -4633,7 +4726,7 @@
         <v>30</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>185</v>
@@ -4674,16 +4767,16 @@
         <v>46192</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>182</v>
@@ -4692,7 +4785,7 @@
         <v>183</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>15</v>
@@ -4718,16 +4811,16 @@
         <v>46192</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>182</v>
@@ -4736,7 +4829,7 @@
         <v>183</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>15</v>
@@ -4765,7 +4858,7 @@
         <v>30</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>185</v>
@@ -4806,25 +4899,25 @@
         <v>46192</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>15</v>
@@ -4833,7 +4926,7 @@
         <v>1</v>
       </c>
       <c r="K80" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L80" s="4">
         <v>25</v>
@@ -4850,16 +4943,16 @@
         <v>46192</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>182</v>
@@ -4868,7 +4961,7 @@
         <v>183</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>15</v>
@@ -4894,25 +4987,25 @@
         <v>46192</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>15</v>
@@ -4921,7 +5014,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L82" s="4">
         <v>25</v>
@@ -4941,7 +5034,7 @@
         <v>30</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>185</v>
@@ -4982,16 +5075,16 @@
         <v>46192</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>182</v>
@@ -5000,7 +5093,7 @@
         <v>183</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>15</v>
@@ -5026,16 +5119,16 @@
         <v>46192</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>182</v>
@@ -5044,7 +5137,7 @@
         <v>183</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>15</v>
@@ -5070,25 +5163,25 @@
         <v>46192</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>15</v>
@@ -5097,7 +5190,7 @@
         <v>1</v>
       </c>
       <c r="K86" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L86" s="4">
         <v>25</v>
@@ -5114,16 +5207,16 @@
         <v>46192</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>182</v>
@@ -5132,7 +5225,7 @@
         <v>183</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>15</v>
@@ -5158,16 +5251,16 @@
         <v>46192</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>182</v>
@@ -5176,7 +5269,7 @@
         <v>183</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>15</v>
@@ -5202,25 +5295,25 @@
         <v>46192</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>15</v>
@@ -5229,7 +5322,7 @@
         <v>1</v>
       </c>
       <c r="K89" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L89" s="4">
         <v>25</v>
@@ -5249,7 +5342,7 @@
         <v>30</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>185</v>
@@ -5290,16 +5383,16 @@
         <v>46192</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>182</v>
@@ -5308,7 +5401,7 @@
         <v>183</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>15</v>
@@ -5337,7 +5430,7 @@
         <v>30</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>185</v>
@@ -5378,25 +5471,25 @@
         <v>46192</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>15</v>
@@ -5405,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="K93" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L93" s="4">
         <v>25</v>
@@ -5422,16 +5515,16 @@
         <v>46192</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>182</v>
@@ -5440,7 +5533,7 @@
         <v>183</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>15</v>
@@ -5466,16 +5559,16 @@
         <v>46192</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>182</v>
@@ -5484,7 +5577,7 @@
         <v>183</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>15</v>
@@ -5510,16 +5603,16 @@
         <v>46192</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>182</v>
@@ -5528,7 +5621,7 @@
         <v>183</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>15</v>
@@ -5557,7 +5650,7 @@
         <v>30</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>185</v>
@@ -5601,7 +5694,7 @@
         <v>30</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>185</v>
@@ -5645,7 +5738,7 @@
         <v>30</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>185</v>
@@ -5689,7 +5782,7 @@
         <v>18</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>181</v>
@@ -5730,16 +5823,16 @@
         <v>46192</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>182</v>
@@ -5748,7 +5841,7 @@
         <v>183</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>15</v>
@@ -5774,16 +5867,16 @@
         <v>46192</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>182</v>
@@ -5792,7 +5885,7 @@
         <v>183</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>15</v>
@@ -5821,7 +5914,7 @@
         <v>30</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>185</v>
@@ -5862,16 +5955,16 @@
         <v>46192</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>182</v>
@@ -5880,7 +5973,7 @@
         <v>183</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>15</v>
@@ -5909,7 +6002,7 @@
         <v>30</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>185</v>
@@ -5953,7 +6046,7 @@
         <v>30</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>185</v>
@@ -5997,7 +6090,7 @@
         <v>18</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>181</v>
@@ -6038,25 +6131,25 @@
         <v>46192</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>15</v>
@@ -6065,7 +6158,7 @@
         <v>1</v>
       </c>
       <c r="K108" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L108" s="4">
         <v>25</v>
@@ -6085,7 +6178,7 @@
         <v>18</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>181</v>
@@ -6126,16 +6219,16 @@
         <v>46192</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>182</v>
@@ -6144,7 +6237,7 @@
         <v>183</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>15</v>
@@ -6173,7 +6266,7 @@
         <v>18</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>181</v>
@@ -6217,7 +6310,7 @@
         <v>30</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>185</v>
@@ -6261,7 +6354,7 @@
         <v>30</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>185</v>
@@ -6302,16 +6395,16 @@
         <v>46192</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>182</v>
@@ -6320,7 +6413,7 @@
         <v>183</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>15</v>
@@ -6346,25 +6439,25 @@
         <v>46192</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>15</v>
@@ -6373,7 +6466,7 @@
         <v>1</v>
       </c>
       <c r="K115" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L115" s="4">
         <v>25</v>
@@ -6393,7 +6486,7 @@
         <v>18</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>181</v>
@@ -6437,7 +6530,7 @@
         <v>18</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>181</v>
@@ -6481,7 +6574,7 @@
         <v>18</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>181</v>
@@ -6522,16 +6615,16 @@
         <v>46192</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>182</v>
@@ -6540,7 +6633,7 @@
         <v>183</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
@@ -6566,16 +6659,16 @@
         <v>46192</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>182</v>
@@ -6584,7 +6677,7 @@
         <v>183</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>15</v>
@@ -6610,16 +6703,16 @@
         <v>46192</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>182</v>
@@ -6628,7 +6721,7 @@
         <v>183</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>15</v>
@@ -6657,7 +6750,7 @@
         <v>18</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>181</v>
@@ -6701,7 +6794,7 @@
         <v>18</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>181</v>
@@ -6745,7 +6838,7 @@
         <v>18</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>181</v>
@@ -6783,19 +6876,19 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>182</v>
@@ -6804,7 +6897,7 @@
         <v>183</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
@@ -6827,28 +6920,28 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
@@ -6857,7 +6950,7 @@
         <v>1</v>
       </c>
       <c r="K126" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L126" s="4">
         <v>25</v>
@@ -6871,19 +6964,19 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>182</v>
@@ -6892,7 +6985,7 @@
         <v>183</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
@@ -6915,13 +7008,13 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>181</v>
@@ -6959,19 +7052,19 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>182</v>
@@ -6980,7 +7073,7 @@
         <v>183</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>15</v>
@@ -7003,19 +7096,19 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>182</v>
@@ -7024,7 +7117,7 @@
         <v>183</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
@@ -7047,19 +7140,19 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
-        <v>46193</v>
+        <v>46192</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>182</v>
@@ -7068,7 +7161,7 @@
         <v>183</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>15</v>
@@ -7097,7 +7190,7 @@
         <v>30</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>185</v>
@@ -7138,25 +7231,25 @@
         <v>46193</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
@@ -7165,7 +7258,7 @@
         <v>1</v>
       </c>
       <c r="K133" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L133" s="4">
         <v>25</v>
@@ -7185,7 +7278,7 @@
         <v>30</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>185</v>
@@ -7226,16 +7319,16 @@
         <v>46193</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>182</v>
@@ -7244,7 +7337,7 @@
         <v>183</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
@@ -7270,16 +7363,16 @@
         <v>46193</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>182</v>
@@ -7288,7 +7381,7 @@
         <v>183</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>15</v>
@@ -7314,16 +7407,16 @@
         <v>46193</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>182</v>
@@ -7332,7 +7425,7 @@
         <v>183</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>15</v>
@@ -7361,7 +7454,7 @@
         <v>30</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>185</v>
@@ -7405,7 +7498,7 @@
         <v>30</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>185</v>
@@ -7446,16 +7539,16 @@
         <v>46193</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>182</v>
@@ -7464,7 +7557,7 @@
         <v>183</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>15</v>
@@ -7493,7 +7586,7 @@
         <v>30</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>185</v>
@@ -7534,16 +7627,16 @@
         <v>46193</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>182</v>
@@ -7552,7 +7645,7 @@
         <v>183</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>15</v>
@@ -7578,16 +7671,16 @@
         <v>46193</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>182</v>
@@ -7596,7 +7689,7 @@
         <v>183</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>15</v>
@@ -7625,7 +7718,7 @@
         <v>18</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>181</v>
@@ -7666,16 +7759,16 @@
         <v>46193</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>182</v>
@@ -7684,7 +7777,7 @@
         <v>183</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>15</v>
@@ -7710,16 +7803,16 @@
         <v>46193</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>182</v>
@@ -7728,7 +7821,7 @@
         <v>183</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>15</v>
@@ -7754,16 +7847,16 @@
         <v>46193</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>182</v>
@@ -7772,7 +7865,7 @@
         <v>183</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>15</v>
@@ -7798,16 +7891,16 @@
         <v>46193</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>182</v>
@@ -7816,7 +7909,7 @@
         <v>183</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>15</v>
@@ -7845,7 +7938,7 @@
         <v>18</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>181</v>
@@ -7889,7 +7982,7 @@
         <v>30</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>185</v>
@@ -7933,7 +8026,7 @@
         <v>18</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>181</v>
@@ -7977,7 +8070,7 @@
         <v>18</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>181</v>
@@ -8021,7 +8114,7 @@
         <v>18</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>181</v>
@@ -8062,25 +8155,25 @@
         <v>46193</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>15</v>
@@ -8089,7 +8182,7 @@
         <v>1</v>
       </c>
       <c r="K154" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L154" s="4">
         <v>25</v>
@@ -8109,7 +8202,7 @@
         <v>18</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>181</v>
@@ -8153,7 +8246,7 @@
         <v>18</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>181</v>
@@ -8194,16 +8287,16 @@
         <v>46193</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>182</v>
@@ -8212,7 +8305,7 @@
         <v>183</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>15</v>
@@ -8241,7 +8334,7 @@
         <v>18</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>181</v>
@@ -8282,16 +8375,16 @@
         <v>46193</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>182</v>
@@ -8300,7 +8393,7 @@
         <v>183</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>15</v>
@@ -8326,25 +8419,25 @@
         <v>46193</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>15</v>
@@ -8353,7 +8446,7 @@
         <v>1</v>
       </c>
       <c r="K160" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L160" s="4">
         <v>25</v>
@@ -8373,7 +8466,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>177</v>
@@ -8417,7 +8510,7 @@
         <v>18</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>181</v>
@@ -8461,7 +8554,7 @@
         <v>18</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>181</v>
@@ -8505,7 +8598,7 @@
         <v>18</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>181</v>
@@ -8549,7 +8642,7 @@
         <v>18</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>181</v>
@@ -8590,16 +8683,16 @@
         <v>46193</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>182</v>
@@ -8608,7 +8701,7 @@
         <v>183</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I166" s="3" t="s">
         <v>15</v>
@@ -8634,25 +8727,25 @@
         <v>46193</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I167" s="3" t="s">
         <v>15</v>
@@ -8661,7 +8754,7 @@
         <v>1</v>
       </c>
       <c r="K167" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L167" s="4">
         <v>25</v>
@@ -8678,25 +8771,25 @@
         <v>46193</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I168" s="3" t="s">
         <v>15</v>
@@ -8705,7 +8798,7 @@
         <v>1</v>
       </c>
       <c r="K168" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L168" s="4">
         <v>25</v>
@@ -8725,7 +8818,7 @@
         <v>18</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>181</v>
@@ -8769,7 +8862,7 @@
         <v>18</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>181</v>
@@ -8813,7 +8906,7 @@
         <v>18</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>181</v>
@@ -8857,7 +8950,7 @@
         <v>18</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>181</v>
@@ -8901,7 +8994,7 @@
         <v>18</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>181</v>
@@ -8945,7 +9038,7 @@
         <v>18</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>181</v>
@@ -8989,7 +9082,7 @@
         <v>18</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>181</v>
@@ -9030,25 +9123,25 @@
         <v>46193</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I176" s="3" t="s">
         <v>15</v>
@@ -9057,7 +9150,7 @@
         <v>1</v>
       </c>
       <c r="K176" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L176" s="4">
         <v>25</v>
@@ -9077,7 +9170,7 @@
         <v>18</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>181</v>
@@ -9115,19 +9208,19 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>182</v>
@@ -9136,7 +9229,7 @@
         <v>183</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I178" s="3" t="s">
         <v>15</v>
@@ -9159,19 +9252,19 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>182</v>
@@ -9180,7 +9273,7 @@
         <v>183</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I179" s="3" t="s">
         <v>15</v>
@@ -9203,19 +9296,19 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>182</v>
@@ -9224,7 +9317,7 @@
         <v>183</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I180" s="3" t="s">
         <v>15</v>
@@ -9247,28 +9340,28 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I181" s="3" t="s">
         <v>15</v>
@@ -9277,7 +9370,7 @@
         <v>1</v>
       </c>
       <c r="K181" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L181" s="4">
         <v>25</v>
@@ -9291,13 +9384,13 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>181</v>
@@ -9335,28 +9428,28 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I183" s="3" t="s">
         <v>15</v>
@@ -9365,7 +9458,7 @@
         <v>1</v>
       </c>
       <c r="K183" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L183" s="4">
         <v>25</v>
@@ -9379,13 +9472,13 @@
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="5">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>181</v>
@@ -9429,7 +9522,7 @@
         <v>30</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="D185" s="3" t="s">
         <v>185</v>
@@ -9473,7 +9566,7 @@
         <v>30</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>185</v>
@@ -9514,16 +9607,16 @@
         <v>46196</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>182</v>
@@ -9532,7 +9625,7 @@
         <v>183</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I187" s="3" t="s">
         <v>15</v>
@@ -9561,7 +9654,7 @@
         <v>13</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>177</v>
@@ -9605,7 +9698,7 @@
         <v>18</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>181</v>
@@ -9646,16 +9739,16 @@
         <v>46196</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>182</v>
@@ -9664,7 +9757,7 @@
         <v>183</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I190" s="3" t="s">
         <v>15</v>
@@ -9690,16 +9783,16 @@
         <v>46196</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>182</v>
@@ -9708,7 +9801,7 @@
         <v>183</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I191" s="3" t="s">
         <v>15</v>
@@ -9734,16 +9827,16 @@
         <v>46196</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>182</v>
@@ -9752,7 +9845,7 @@
         <v>183</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I192" s="3" t="s">
         <v>15</v>
@@ -9778,16 +9871,16 @@
         <v>46196</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>182</v>
@@ -9796,7 +9889,7 @@
         <v>183</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I193" s="3" t="s">
         <v>15</v>
@@ -9822,16 +9915,16 @@
         <v>46196</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>182</v>
@@ -9840,7 +9933,7 @@
         <v>183</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I194" s="3" t="s">
         <v>15</v>
@@ -9866,25 +9959,25 @@
         <v>46196</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>15</v>
@@ -9893,7 +9986,7 @@
         <v>1</v>
       </c>
       <c r="K195" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L195" s="4">
         <v>25</v>
@@ -9913,7 +10006,7 @@
         <v>18</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D196" s="3" t="s">
         <v>181</v>
@@ -9954,16 +10047,16 @@
         <v>46196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>182</v>
@@ -9972,7 +10065,7 @@
         <v>183</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I197" s="3" t="s">
         <v>15</v>
@@ -9998,16 +10091,16 @@
         <v>46196</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>182</v>
@@ -10016,7 +10109,7 @@
         <v>183</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I198" s="3" t="s">
         <v>15</v>
@@ -10045,7 +10138,7 @@
         <v>18</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>181</v>
@@ -10086,16 +10179,16 @@
         <v>46196</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>182</v>
@@ -10104,7 +10197,7 @@
         <v>183</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I200" s="3" t="s">
         <v>15</v>
@@ -10133,7 +10226,7 @@
         <v>30</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D201" s="3" t="s">
         <v>185</v>
@@ -10174,16 +10267,16 @@
         <v>46196</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>182</v>
@@ -10192,7 +10285,7 @@
         <v>183</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I202" s="3" t="s">
         <v>15</v>
@@ -10218,16 +10311,16 @@
         <v>46196</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>182</v>
@@ -10236,7 +10329,7 @@
         <v>183</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="I203" s="3" t="s">
         <v>15</v>
@@ -10265,7 +10358,7 @@
         <v>18</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>181</v>
@@ -10306,25 +10399,25 @@
         <v>46196</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I205" s="3" t="s">
         <v>15</v>
@@ -10333,7 +10426,7 @@
         <v>1</v>
       </c>
       <c r="K205" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L205" s="4">
         <v>25</v>
@@ -10350,25 +10443,25 @@
         <v>46196</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I206" s="3" t="s">
         <v>15</v>
@@ -10377,7 +10470,7 @@
         <v>1</v>
       </c>
       <c r="K206" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L206" s="4">
         <v>25</v>
@@ -10394,25 +10487,25 @@
         <v>46196</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="I207" s="3" t="s">
         <v>15</v>
@@ -10421,7 +10514,7 @@
         <v>1</v>
       </c>
       <c r="K207" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L207" s="4">
         <v>25</v>
@@ -10438,16 +10531,16 @@
         <v>46196</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>182</v>
@@ -10456,7 +10549,7 @@
         <v>183</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I208" s="3" t="s">
         <v>15</v>
@@ -10482,16 +10575,16 @@
         <v>46196</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>182</v>
@@ -10500,7 +10593,7 @@
         <v>183</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I209" s="3" t="s">
         <v>15</v>
@@ -10526,16 +10619,16 @@
         <v>46196</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>182</v>
@@ -10544,7 +10637,7 @@
         <v>183</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I210" s="3" t="s">
         <v>15</v>
@@ -10573,7 +10666,7 @@
         <v>18</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D211" s="3" t="s">
         <v>181</v>
@@ -10611,28 +10704,28 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" s="5">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I212" s="3" t="s">
         <v>15</v>
@@ -10641,7 +10734,7 @@
         <v>1</v>
       </c>
       <c r="K212" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L212" s="4">
         <v>25</v>
@@ -10655,28 +10748,28 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="I213" s="3" t="s">
         <v>15</v>
@@ -10685,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="K213" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L213" s="4">
         <v>25</v>
@@ -10699,28 +10792,28 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I214" s="3" t="s">
         <v>15</v>
@@ -10729,7 +10822,7 @@
         <v>1</v>
       </c>
       <c r="K214" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L214" s="4">
         <v>25</v>
@@ -10743,13 +10836,13 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>181</v>
@@ -10787,28 +10880,28 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I216" s="3" t="s">
         <v>15</v>
@@ -10817,7 +10910,7 @@
         <v>1</v>
       </c>
       <c r="K216" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L216" s="4">
         <v>25</v>
@@ -10831,28 +10924,28 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I217" s="3" t="s">
         <v>15</v>
@@ -10861,7 +10954,7 @@
         <v>1</v>
       </c>
       <c r="K217" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L217" s="4">
         <v>25</v>
@@ -10875,13 +10968,13 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>181</v>
@@ -10925,7 +11018,7 @@
         <v>18</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D219" s="3" t="s">
         <v>181</v>
@@ -10966,16 +11059,16 @@
         <v>46197</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>182</v>
@@ -10984,7 +11077,7 @@
         <v>183</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="I220" s="3" t="s">
         <v>15</v>
@@ -11013,7 +11106,7 @@
         <v>18</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D221" s="3" t="s">
         <v>181</v>
@@ -11057,7 +11150,7 @@
         <v>18</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D222" s="3" t="s">
         <v>181</v>
@@ -11098,25 +11191,25 @@
         <v>46197</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I223" s="3" t="s">
         <v>15</v>
@@ -11125,7 +11218,7 @@
         <v>1</v>
       </c>
       <c r="K223" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L223" s="4">
         <v>25</v>
@@ -11142,25 +11235,25 @@
         <v>46197</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I224" s="3" t="s">
         <v>15</v>
@@ -11169,7 +11262,7 @@
         <v>1</v>
       </c>
       <c r="K224" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L224" s="4">
         <v>25</v>
@@ -11186,25 +11279,25 @@
         <v>46197</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I225" s="3" t="s">
         <v>15</v>
@@ -11213,7 +11306,7 @@
         <v>1</v>
       </c>
       <c r="K225" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L225" s="4">
         <v>25</v>
@@ -11233,7 +11326,7 @@
         <v>18</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>181</v>
@@ -11277,7 +11370,7 @@
         <v>18</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>181</v>
@@ -11318,25 +11411,25 @@
         <v>46197</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I228" s="3" t="s">
         <v>15</v>
@@ -11345,7 +11438,7 @@
         <v>1</v>
       </c>
       <c r="K228" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L228" s="4">
         <v>25</v>
@@ -11362,25 +11455,25 @@
         <v>46197</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I229" s="3" t="s">
         <v>15</v>
@@ -11389,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="K229" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L229" s="4">
         <v>25</v>
@@ -11409,7 +11502,7 @@
         <v>18</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>181</v>
@@ -11453,7 +11546,7 @@
         <v>18</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>181</v>
@@ -11497,7 +11590,7 @@
         <v>13</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D232" s="3" t="s">
         <v>177</v>
@@ -11541,7 +11634,7 @@
         <v>18</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>181</v>
@@ -11579,13 +11672,13 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" s="5">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>181</v>
@@ -11623,28 +11716,28 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I235" s="3" t="s">
         <v>15</v>
@@ -11653,7 +11746,7 @@
         <v>1</v>
       </c>
       <c r="K235" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L235" s="4">
         <v>25</v>
@@ -11667,45 +11760,1585 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H236" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J236" s="4">
+        <v>1</v>
+      </c>
+      <c r="K236" s="4">
+        <v>4</v>
+      </c>
+      <c r="L236" s="4">
+        <v>25</v>
+      </c>
+      <c r="M236" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N236" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A237" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H237" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J237" s="4">
+        <v>1</v>
+      </c>
+      <c r="K237" s="4">
+        <v>6</v>
+      </c>
+      <c r="L237" s="4">
+        <v>25</v>
+      </c>
+      <c r="M237" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N237" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A238" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H238" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J238" s="4">
+        <v>1</v>
+      </c>
+      <c r="K238" s="4">
+        <v>6</v>
+      </c>
+      <c r="L238" s="4">
+        <v>25</v>
+      </c>
+      <c r="M238" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N238" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A239" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H239" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I239" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J239" s="4">
+        <v>1</v>
+      </c>
+      <c r="K239" s="4">
+        <v>4</v>
+      </c>
+      <c r="L239" s="4">
+        <v>25</v>
+      </c>
+      <c r="M239" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N239" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A240" s="5">
+        <v>46197</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H240" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J240" s="4">
+        <v>1</v>
+      </c>
+      <c r="K240" s="4">
+        <v>6</v>
+      </c>
+      <c r="L240" s="4">
+        <v>25</v>
+      </c>
+      <c r="M240" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N240" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A241" s="5">
         <v>46198</v>
       </c>
-      <c r="B236" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C236" s="3" t="s">
+      <c r="B241" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H241" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J241" s="4">
+        <v>1</v>
+      </c>
+      <c r="K241" s="4">
+        <v>6</v>
+      </c>
+      <c r="L241" s="4">
+        <v>25</v>
+      </c>
+      <c r="M241" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N241" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A242" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H242" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I242" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J242" s="4">
+        <v>1</v>
+      </c>
+      <c r="K242" s="4">
+        <v>6</v>
+      </c>
+      <c r="L242" s="4">
+        <v>25</v>
+      </c>
+      <c r="M242" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N242" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A243" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C243" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D236" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E236" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F236" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G236" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H236" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I236" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J236" s="4">
-        <v>1</v>
-      </c>
-      <c r="K236" s="4">
-        <v>6</v>
-      </c>
-      <c r="L236" s="4">
-        <v>25</v>
-      </c>
-      <c r="M236" s="4">
-        <v>21.75</v>
-      </c>
-      <c r="N236" s="4">
+      <c r="D243" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J243" s="4">
+        <v>1</v>
+      </c>
+      <c r="K243" s="4">
+        <v>6</v>
+      </c>
+      <c r="L243" s="4">
+        <v>25</v>
+      </c>
+      <c r="M243" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N243" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A244" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H244" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I244" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J244" s="4">
+        <v>1</v>
+      </c>
+      <c r="K244" s="4">
+        <v>6</v>
+      </c>
+      <c r="L244" s="4">
+        <v>25</v>
+      </c>
+      <c r="M244" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N244" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A245" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H245" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J245" s="4">
+        <v>1</v>
+      </c>
+      <c r="K245" s="4">
+        <v>6</v>
+      </c>
+      <c r="L245" s="4">
+        <v>25</v>
+      </c>
+      <c r="M245" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N245" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A246" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H246" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I246" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J246" s="4">
+        <v>1</v>
+      </c>
+      <c r="K246" s="4">
+        <v>6</v>
+      </c>
+      <c r="L246" s="4">
+        <v>25</v>
+      </c>
+      <c r="M246" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N246" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A247" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H247" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J247" s="4">
+        <v>1</v>
+      </c>
+      <c r="K247" s="4">
+        <v>6</v>
+      </c>
+      <c r="L247" s="4">
+        <v>25</v>
+      </c>
+      <c r="M247" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N247" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A248" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H248" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I248" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J248" s="4">
+        <v>1</v>
+      </c>
+      <c r="K248" s="4">
+        <v>4</v>
+      </c>
+      <c r="L248" s="4">
+        <v>25</v>
+      </c>
+      <c r="M248" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N248" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A249" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H249" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I249" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J249" s="4">
+        <v>1</v>
+      </c>
+      <c r="K249" s="4">
+        <v>4</v>
+      </c>
+      <c r="L249" s="4">
+        <v>25</v>
+      </c>
+      <c r="M249" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N249" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A250" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H250" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I250" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J250" s="4">
+        <v>1</v>
+      </c>
+      <c r="K250" s="4">
+        <v>4</v>
+      </c>
+      <c r="L250" s="4">
+        <v>25</v>
+      </c>
+      <c r="M250" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N250" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A251" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H251" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I251" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J251" s="4">
+        <v>1</v>
+      </c>
+      <c r="K251" s="4">
+        <v>6</v>
+      </c>
+      <c r="L251" s="4">
+        <v>25</v>
+      </c>
+      <c r="M251" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N251" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A252" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H252" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I252" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J252" s="4">
+        <v>1</v>
+      </c>
+      <c r="K252" s="4">
+        <v>6</v>
+      </c>
+      <c r="L252" s="4">
+        <v>25</v>
+      </c>
+      <c r="M252" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N252" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A253" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H253" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I253" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J253" s="4">
+        <v>1</v>
+      </c>
+      <c r="K253" s="4">
+        <v>6</v>
+      </c>
+      <c r="L253" s="4">
+        <v>25</v>
+      </c>
+      <c r="M253" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N253" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A254" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H254" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I254" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J254" s="4">
+        <v>1</v>
+      </c>
+      <c r="K254" s="4">
+        <v>6</v>
+      </c>
+      <c r="L254" s="4">
+        <v>25</v>
+      </c>
+      <c r="M254" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N254" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A255" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H255" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I255" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J255" s="4">
+        <v>1</v>
+      </c>
+      <c r="K255" s="4">
+        <v>6</v>
+      </c>
+      <c r="L255" s="4">
+        <v>25</v>
+      </c>
+      <c r="M255" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N255" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A256" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H256" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I256" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J256" s="4">
+        <v>1</v>
+      </c>
+      <c r="K256" s="4">
+        <v>6</v>
+      </c>
+      <c r="L256" s="4">
+        <v>25</v>
+      </c>
+      <c r="M256" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N256" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A257" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H257" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I257" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J257" s="4">
+        <v>1</v>
+      </c>
+      <c r="K257" s="4">
+        <v>6</v>
+      </c>
+      <c r="L257" s="4">
+        <v>25</v>
+      </c>
+      <c r="M257" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N257" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A258" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H258" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I258" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J258" s="4">
+        <v>1</v>
+      </c>
+      <c r="K258" s="4">
+        <v>6</v>
+      </c>
+      <c r="L258" s="4">
+        <v>25</v>
+      </c>
+      <c r="M258" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N258" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A259" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H259" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I259" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J259" s="4">
+        <v>1</v>
+      </c>
+      <c r="K259" s="4">
+        <v>6</v>
+      </c>
+      <c r="L259" s="4">
+        <v>25</v>
+      </c>
+      <c r="M259" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N259" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A260" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H260" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I260" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J260" s="4">
+        <v>1</v>
+      </c>
+      <c r="K260" s="4">
+        <v>6</v>
+      </c>
+      <c r="L260" s="4">
+        <v>25</v>
+      </c>
+      <c r="M260" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N260" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A261" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H261" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I261" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J261" s="4">
+        <v>1</v>
+      </c>
+      <c r="K261" s="4">
+        <v>6</v>
+      </c>
+      <c r="L261" s="4">
+        <v>25</v>
+      </c>
+      <c r="M261" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N261" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A262" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H262" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I262" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J262" s="4">
+        <v>1</v>
+      </c>
+      <c r="K262" s="4">
+        <v>6</v>
+      </c>
+      <c r="L262" s="4">
+        <v>25</v>
+      </c>
+      <c r="M262" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N262" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A263" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H263" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I263" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J263" s="4">
+        <v>1</v>
+      </c>
+      <c r="K263" s="4">
+        <v>6</v>
+      </c>
+      <c r="L263" s="4">
+        <v>25</v>
+      </c>
+      <c r="M263" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N263" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A264" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H264" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I264" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J264" s="4">
+        <v>1</v>
+      </c>
+      <c r="K264" s="4">
+        <v>6</v>
+      </c>
+      <c r="L264" s="4">
+        <v>25</v>
+      </c>
+      <c r="M264" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N264" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A265" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G265" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H265" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I265" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J265" s="4">
+        <v>1</v>
+      </c>
+      <c r="K265" s="4">
+        <v>6</v>
+      </c>
+      <c r="L265" s="4">
+        <v>25</v>
+      </c>
+      <c r="M265" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N265" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A266" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G266" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H266" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I266" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J266" s="4">
+        <v>1</v>
+      </c>
+      <c r="K266" s="4">
+        <v>6</v>
+      </c>
+      <c r="L266" s="4">
+        <v>25</v>
+      </c>
+      <c r="M266" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N266" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A267" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H267" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I267" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J267" s="4">
+        <v>1</v>
+      </c>
+      <c r="K267" s="4">
+        <v>6</v>
+      </c>
+      <c r="L267" s="4">
+        <v>25</v>
+      </c>
+      <c r="M267" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N267" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A268" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H268" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I268" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J268" s="4">
+        <v>1</v>
+      </c>
+      <c r="K268" s="4">
+        <v>6</v>
+      </c>
+      <c r="L268" s="4">
+        <v>25</v>
+      </c>
+      <c r="M268" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N268" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A269" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H269" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I269" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J269" s="4">
+        <v>1</v>
+      </c>
+      <c r="K269" s="4">
+        <v>6</v>
+      </c>
+      <c r="L269" s="4">
+        <v>25</v>
+      </c>
+      <c r="M269" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N269" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A270" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H270" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I270" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J270" s="4">
+        <v>1</v>
+      </c>
+      <c r="K270" s="4">
+        <v>6</v>
+      </c>
+      <c r="L270" s="4">
+        <v>25</v>
+      </c>
+      <c r="M270" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N270" s="4">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A271" s="5">
+        <v>46198</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H271" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I271" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J271" s="4">
+        <v>1</v>
+      </c>
+      <c r="K271" s="4">
+        <v>6</v>
+      </c>
+      <c r="L271" s="4">
+        <v>25</v>
+      </c>
+      <c r="M271" s="4">
+        <v>21.75</v>
+      </c>
+      <c r="N271" s="4">
         <v>0.75</v>
       </c>
     </row>
